--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K509"/>
+  <dimension ref="A1:K510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20277,6 +20277,45 @@
       <c r="K509" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>312.58</v>
+      </c>
+      <c r="C510" t="n">
+        <v>308.7</v>
+      </c>
+      <c r="D510" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="E510" t="n">
+        <v>316.89</v>
+      </c>
+      <c r="F510" t="n">
+        <v>315.24</v>
+      </c>
+      <c r="G510" t="n">
+        <v>306.53</v>
+      </c>
+      <c r="H510" t="n">
+        <v>304.67</v>
+      </c>
+      <c r="I510" t="n">
+        <v>303.27</v>
+      </c>
+      <c r="J510" t="n">
+        <v>306.61</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B535"/>
+  <dimension ref="A1:B536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25644,6 +25683,16 @@
       </c>
       <c r="B535" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -25812,28 +25861,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4255777926453008</v>
+        <v>-0.4245400529432469</v>
       </c>
       <c r="J2" t="n">
+        <v>509</v>
+      </c>
+      <c r="K2" t="n">
         <v>508</v>
       </c>
-      <c r="K2" t="n">
-        <v>507</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2099914090930909</v>
+        <v>0.2098234617601521</v>
       </c>
       <c r="M2" t="n">
-        <v>4.328326287276778</v>
+        <v>4.32362111228205</v>
       </c>
       <c r="N2" t="n">
-        <v>37.29678619165114</v>
+        <v>37.2372610708566</v>
       </c>
       <c r="O2" t="n">
-        <v>6.107109479258673</v>
+        <v>6.102234104887865</v>
       </c>
       <c r="P2" t="n">
-        <v>321.1406227094771</v>
+        <v>321.129767441515</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25890,28 +25939,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1721270145636026</v>
+        <v>-0.1712475120080687</v>
       </c>
       <c r="J3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K3" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0653755185124496</v>
+        <v>0.06498268476870084</v>
       </c>
       <c r="M3" t="n">
-        <v>3.779319918279616</v>
+        <v>3.776240534061311</v>
       </c>
       <c r="N3" t="n">
-        <v>23.33893346770571</v>
+        <v>23.30315697958897</v>
       </c>
       <c r="O3" t="n">
-        <v>4.831038549598389</v>
+        <v>4.827334355479115</v>
       </c>
       <c r="P3" t="n">
-        <v>310.9700717377056</v>
+        <v>310.9609155009843</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25968,28 +26017,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2504029764995548</v>
+        <v>-0.2486924000984328</v>
       </c>
       <c r="J4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K4" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1198125079021961</v>
+        <v>0.1186591661481277</v>
       </c>
       <c r="M4" t="n">
-        <v>4.022531481068732</v>
+        <v>4.023344065701431</v>
       </c>
       <c r="N4" t="n">
-        <v>25.38124579798352</v>
+        <v>25.36949626263221</v>
       </c>
       <c r="O4" t="n">
-        <v>5.037980329257302</v>
+        <v>5.036814098478542</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6816630601147</v>
+        <v>330.6638547634134</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26046,28 +26095,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.277640894973942</v>
+        <v>-0.2759945916370107</v>
       </c>
       <c r="J5" t="n">
+        <v>509</v>
+      </c>
+      <c r="K5" t="n">
         <v>508</v>
       </c>
-      <c r="K5" t="n">
-        <v>507</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1380834929687778</v>
+        <v>0.1370155681389622</v>
       </c>
       <c r="M5" t="n">
-        <v>4.058515142628048</v>
+        <v>4.058978019831561</v>
       </c>
       <c r="N5" t="n">
-        <v>26.54673524534855</v>
+        <v>26.52985994522028</v>
       </c>
       <c r="O5" t="n">
-        <v>5.152352399181227</v>
+        <v>5.150714508223134</v>
       </c>
       <c r="P5" t="n">
-        <v>319.9608866673586</v>
+        <v>319.9437506432821</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26124,28 +26173,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2003865562512128</v>
+        <v>-0.1990429107003037</v>
       </c>
       <c r="J6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K6" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07963753892153869</v>
+        <v>0.07889628680874539</v>
       </c>
       <c r="M6" t="n">
-        <v>4.173617426291769</v>
+        <v>4.171356078688157</v>
       </c>
       <c r="N6" t="n">
-        <v>25.76335966958638</v>
+        <v>25.73608498250868</v>
       </c>
       <c r="O6" t="n">
-        <v>5.075761979209267</v>
+        <v>5.073074509851859</v>
       </c>
       <c r="P6" t="n">
-        <v>317.0513097474072</v>
+        <v>317.0373633281392</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26202,28 +26251,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0471032767780346</v>
+        <v>-0.04597915114667362</v>
       </c>
       <c r="J7" t="n">
+        <v>509</v>
+      </c>
+      <c r="K7" t="n">
         <v>508</v>
       </c>
-      <c r="K7" t="n">
-        <v>507</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001682221356605562</v>
+        <v>0.001609429988830957</v>
       </c>
       <c r="M7" t="n">
-        <v>6.743341651438869</v>
+        <v>6.734644852555791</v>
       </c>
       <c r="N7" t="n">
-        <v>72.68701400813393</v>
+        <v>72.56042917602065</v>
       </c>
       <c r="O7" t="n">
-        <v>8.525667950849009</v>
+        <v>8.518240967243216</v>
       </c>
       <c r="P7" t="n">
-        <v>304.8715251681322</v>
+        <v>304.8598307307711</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26280,28 +26329,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05583217415885042</v>
+        <v>0.05723439824531556</v>
       </c>
       <c r="J8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K8" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003246881938813728</v>
+        <v>0.003424193410177967</v>
       </c>
       <c r="M8" t="n">
-        <v>5.895607654601718</v>
+        <v>5.889476519066823</v>
       </c>
       <c r="N8" t="n">
-        <v>52.92606970489655</v>
+        <v>52.84741385438365</v>
       </c>
       <c r="O8" t="n">
-        <v>7.275030563846213</v>
+        <v>7.269622676204292</v>
       </c>
       <c r="P8" t="n">
-        <v>299.5774480112111</v>
+        <v>299.5628711691846</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26358,28 +26407,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005254587379536858</v>
+        <v>0.007589837058079066</v>
       </c>
       <c r="J9" t="n">
+        <v>509</v>
+      </c>
+      <c r="K9" t="n">
         <v>508</v>
       </c>
-      <c r="K9" t="n">
-        <v>507</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.238700945815907e-05</v>
+        <v>2.593822425667192e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>9.352199981337813</v>
+        <v>9.3437254187637</v>
       </c>
       <c r="N9" t="n">
-        <v>122.0080812491223</v>
+        <v>121.8382651740933</v>
       </c>
       <c r="O9" t="n">
-        <v>11.04572683208861</v>
+        <v>11.03803719753169</v>
       </c>
       <c r="P9" t="n">
-        <v>297.133512757036</v>
+        <v>297.1090848962066</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26436,28 +26485,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1398897852916197</v>
+        <v>0.1401418362917878</v>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K10" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04923801075206913</v>
+        <v>0.04960402758871663</v>
       </c>
       <c r="M10" t="n">
-        <v>3.570402242584163</v>
+        <v>3.564666792407929</v>
       </c>
       <c r="N10" t="n">
-        <v>20.82112762255868</v>
+        <v>20.78104922056127</v>
       </c>
       <c r="O10" t="n">
-        <v>4.563017381356188</v>
+        <v>4.558623610319376</v>
       </c>
       <c r="P10" t="n">
-        <v>302.2749382367062</v>
+        <v>302.2723142095116</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26495,7 +26544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K509"/>
+  <dimension ref="A1:K510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55471,6 +55520,63 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>-46.590793972647994,168.80598286035698</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>-46.59017797581047,168.8060718227776</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>-46.58952670826739,168.80582906797486</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>-46.58893279255208,168.80545750311265</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>-46.58838783659317,168.80497454876982</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>-46.587878239300714,168.80440167587489</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>-46.587440387978084,168.80374846215437</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>-46.587014350711435,168.8030690124964</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>-46.58666017345861,168.8023091680339</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K510"/>
+  <dimension ref="A1:K511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20314,6 +20314,45 @@
         <v>306.61</v>
       </c>
       <c r="K510" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>313.44</v>
+      </c>
+      <c r="C511" t="n">
+        <v>309.91</v>
+      </c>
+      <c r="D511" t="n">
+        <v>330.67</v>
+      </c>
+      <c r="E511" t="n">
+        <v>318.71</v>
+      </c>
+      <c r="F511" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="G511" t="n">
+        <v>308.66</v>
+      </c>
+      <c r="H511" t="n">
+        <v>306.55</v>
+      </c>
+      <c r="I511" t="n">
+        <v>305.05</v>
+      </c>
+      <c r="J511" t="n">
+        <v>307.27</v>
+      </c>
+      <c r="K511" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20330,7 +20369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B536"/>
+  <dimension ref="A1:B537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25693,6 +25732,16 @@
       </c>
       <c r="B536" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -25861,28 +25910,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4245400529432469</v>
+        <v>-0.4231694359881767</v>
       </c>
       <c r="J2" t="n">
+        <v>510</v>
+      </c>
+      <c r="K2" t="n">
         <v>509</v>
       </c>
-      <c r="K2" t="n">
-        <v>508</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2098234617601521</v>
+        <v>0.2093466771738385</v>
       </c>
       <c r="M2" t="n">
-        <v>4.32362111228205</v>
+        <v>4.320129982587588</v>
       </c>
       <c r="N2" t="n">
-        <v>37.2372610708566</v>
+        <v>37.18839839715152</v>
       </c>
       <c r="O2" t="n">
-        <v>6.102234104887865</v>
+        <v>6.09822911976514</v>
       </c>
       <c r="P2" t="n">
-        <v>321.129767441515</v>
+        <v>321.1154022586489</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25939,28 +25988,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1712475120080687</v>
+        <v>-0.1699072948305309</v>
       </c>
       <c r="J3" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K3" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06498268476870084</v>
+        <v>0.06422779944884183</v>
       </c>
       <c r="M3" t="n">
-        <v>3.776240534061311</v>
+        <v>3.775436143593558</v>
       </c>
       <c r="N3" t="n">
-        <v>23.30315697958897</v>
+        <v>23.28091787867759</v>
       </c>
       <c r="O3" t="n">
-        <v>4.827334355479115</v>
+        <v>4.825030350026577</v>
       </c>
       <c r="P3" t="n">
-        <v>310.9609155009843</v>
+        <v>310.946935637848</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26017,28 +26066,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2486924000984328</v>
+        <v>-0.2461521966997332</v>
       </c>
       <c r="J4" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K4" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1186591661481277</v>
+        <v>0.1166220626429448</v>
       </c>
       <c r="M4" t="n">
-        <v>4.023344065701431</v>
+        <v>4.028321466221042</v>
       </c>
       <c r="N4" t="n">
-        <v>25.36949626263221</v>
+        <v>25.40400639221084</v>
       </c>
       <c r="O4" t="n">
-        <v>5.036814098478542</v>
+        <v>5.040238723732323</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6638547634134</v>
+        <v>330.6373577922899</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26095,28 +26144,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2759945916370107</v>
+        <v>-0.2736563379919189</v>
       </c>
       <c r="J5" t="n">
+        <v>510</v>
+      </c>
+      <c r="K5" t="n">
         <v>509</v>
       </c>
-      <c r="K5" t="n">
-        <v>508</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1370155681389622</v>
+        <v>0.1351944493061727</v>
       </c>
       <c r="M5" t="n">
-        <v>4.058978019831561</v>
+        <v>4.063055672637574</v>
       </c>
       <c r="N5" t="n">
-        <v>26.52985994522028</v>
+        <v>26.5492837873646</v>
       </c>
       <c r="O5" t="n">
-        <v>5.150714508223134</v>
+        <v>5.152599711540244</v>
       </c>
       <c r="P5" t="n">
-        <v>319.9437506432821</v>
+        <v>319.9193645492463</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26173,28 +26222,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1990429107003037</v>
+        <v>-0.1969790825398256</v>
       </c>
       <c r="J6" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K6" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07889628680874539</v>
+        <v>0.07754027323401969</v>
       </c>
       <c r="M6" t="n">
-        <v>4.171356078688157</v>
+        <v>4.172275944546541</v>
       </c>
       <c r="N6" t="n">
-        <v>25.73608498250868</v>
+        <v>25.74137021279775</v>
       </c>
       <c r="O6" t="n">
-        <v>5.073074509851859</v>
+        <v>5.073595393091348</v>
       </c>
       <c r="P6" t="n">
-        <v>317.0373633281392</v>
+        <v>317.0158993424091</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26251,28 +26300,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04597915114667362</v>
+        <v>-0.0440429898895334</v>
       </c>
       <c r="J7" t="n">
+        <v>510</v>
+      </c>
+      <c r="K7" t="n">
         <v>509</v>
       </c>
-      <c r="K7" t="n">
-        <v>508</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001609429988830957</v>
+        <v>0.001482180643971209</v>
       </c>
       <c r="M7" t="n">
-        <v>6.734644852555791</v>
+        <v>6.729250261827961</v>
       </c>
       <c r="N7" t="n">
-        <v>72.56042917602065</v>
+        <v>72.46693922909331</v>
       </c>
       <c r="O7" t="n">
-        <v>8.518240967243216</v>
+        <v>8.512751566273581</v>
       </c>
       <c r="P7" t="n">
-        <v>304.8598307307711</v>
+        <v>304.8396490852739</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26329,28 +26378,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05723439824531556</v>
+        <v>0.05935052412634512</v>
       </c>
       <c r="J8" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K8" t="n">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003424193410177967</v>
+        <v>0.003692562878333749</v>
       </c>
       <c r="M8" t="n">
-        <v>5.889476519066823</v>
+        <v>5.886124979859833</v>
       </c>
       <c r="N8" t="n">
-        <v>52.84741385438365</v>
+        <v>52.80213325105596</v>
       </c>
       <c r="O8" t="n">
-        <v>7.269622676204292</v>
+        <v>7.266507637858503</v>
       </c>
       <c r="P8" t="n">
-        <v>299.5628711691846</v>
+        <v>299.5408296848299</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26407,28 +26456,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007589837058079066</v>
+        <v>0.01059611808539598</v>
       </c>
       <c r="J9" t="n">
+        <v>510</v>
+      </c>
+      <c r="K9" t="n">
         <v>509</v>
       </c>
-      <c r="K9" t="n">
-        <v>508</v>
-      </c>
       <c r="L9" t="n">
-        <v>2.593822425667192e-05</v>
+        <v>5.072050063181788e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>9.3437254187637</v>
+        <v>9.338236736469874</v>
       </c>
       <c r="N9" t="n">
-        <v>121.8382651740933</v>
+        <v>121.7157782978529</v>
       </c>
       <c r="O9" t="n">
-        <v>11.03803719753169</v>
+        <v>11.03248740302263</v>
       </c>
       <c r="P9" t="n">
-        <v>297.1090848962066</v>
+        <v>297.077576620649</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26485,28 +26534,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1401418362917878</v>
+        <v>0.140643703435111</v>
       </c>
       <c r="J10" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K10" t="n">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04960402758871663</v>
+        <v>0.05013570922671839</v>
       </c>
       <c r="M10" t="n">
-        <v>3.564666792407929</v>
+        <v>3.560217889467531</v>
       </c>
       <c r="N10" t="n">
-        <v>20.78104922056127</v>
+        <v>20.74359082617702</v>
       </c>
       <c r="O10" t="n">
-        <v>4.558623610319376</v>
+        <v>4.554513237018531</v>
       </c>
       <c r="P10" t="n">
-        <v>302.2723142095116</v>
+        <v>302.2670792117113</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26544,7 +26593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K510"/>
+  <dimension ref="A1:K511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55577,6 +55626,63 @@
         </is>
       </c>
     </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>-46.59079336064357,168.80597168323058</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>-46.59017719799019,168.80605608787297</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>-46.58953122384879,168.80580154573923</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-46.588941059216396,168.80543702828908</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>-46.588397921639945,168.8049547210008</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>-46.58789149226723,168.80438163681248</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>-46.587452511248244,168.80373138917167</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-46.58702638870152,168.80305372808527</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-46.586664784196444,168.8023037544468</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K511"/>
+  <dimension ref="A1:K512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20353,6 +20353,45 @@
         <v>307.27</v>
       </c>
       <c r="K511" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:27+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>313.23</v>
+      </c>
+      <c r="C512" t="n">
+        <v>309.56</v>
+      </c>
+      <c r="D512" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="E512" t="n">
+        <v>318.72</v>
+      </c>
+      <c r="F512" t="n">
+        <v>317.07</v>
+      </c>
+      <c r="G512" t="n">
+        <v>308.5</v>
+      </c>
+      <c r="H512" t="n">
+        <v>306.17</v>
+      </c>
+      <c r="I512" t="n">
+        <v>307.54</v>
+      </c>
+      <c r="J512" t="n">
+        <v>306.94</v>
+      </c>
+      <c r="K512" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20369,7 +20408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B537"/>
+  <dimension ref="A1:B538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25742,6 +25781,16 @@
       </c>
       <c r="B537" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -25910,28 +25959,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4231694359881767</v>
+        <v>-0.4218898824437722</v>
       </c>
       <c r="J2" t="n">
+        <v>511</v>
+      </c>
+      <c r="K2" t="n">
         <v>510</v>
       </c>
-      <c r="K2" t="n">
-        <v>509</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2093466771738385</v>
+        <v>0.2089492168190843</v>
       </c>
       <c r="M2" t="n">
-        <v>4.320129982587588</v>
+        <v>4.316307246768432</v>
       </c>
       <c r="N2" t="n">
-        <v>37.18839839715152</v>
+        <v>37.13677942925308</v>
       </c>
       <c r="O2" t="n">
-        <v>6.09822911976514</v>
+        <v>6.093995358486342</v>
       </c>
       <c r="P2" t="n">
-        <v>321.1154022586489</v>
+        <v>321.1019768683092</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25988,28 +26037,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1699072948305309</v>
+        <v>-0.1687139043417997</v>
       </c>
       <c r="J3" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K3" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06422779944884183</v>
+        <v>0.06358846439958221</v>
       </c>
       <c r="M3" t="n">
-        <v>3.775436143593558</v>
+        <v>3.77398876225385</v>
       </c>
       <c r="N3" t="n">
-        <v>23.28091787867759</v>
+        <v>23.25406429366144</v>
       </c>
       <c r="O3" t="n">
-        <v>4.825030350026577</v>
+        <v>4.822246809699959</v>
       </c>
       <c r="P3" t="n">
-        <v>310.946935637848</v>
+        <v>310.9344736749738</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26066,28 +26115,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2461521966997332</v>
+        <v>-0.2438192758693317</v>
       </c>
       <c r="J4" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K4" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1166220626429448</v>
+        <v>0.1148163936894608</v>
       </c>
       <c r="M4" t="n">
-        <v>4.028321466221042</v>
+        <v>4.032205419813741</v>
       </c>
       <c r="N4" t="n">
-        <v>25.40400639221084</v>
+        <v>25.4257770116725</v>
       </c>
       <c r="O4" t="n">
-        <v>5.040238723732323</v>
+        <v>5.042397942613465</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6373577922899</v>
+        <v>330.6129963003463</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26144,28 +26193,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2736563379919189</v>
+        <v>-0.2713332342204811</v>
       </c>
       <c r="J5" t="n">
+        <v>511</v>
+      </c>
+      <c r="K5" t="n">
         <v>510</v>
       </c>
-      <c r="K5" t="n">
-        <v>509</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1351944493061727</v>
+        <v>0.1333904886813705</v>
       </c>
       <c r="M5" t="n">
-        <v>4.063055672637574</v>
+        <v>4.067082467766141</v>
       </c>
       <c r="N5" t="n">
-        <v>26.5492837873646</v>
+        <v>26.56826457884221</v>
       </c>
       <c r="O5" t="n">
-        <v>5.152599711540244</v>
+        <v>5.154441247976566</v>
       </c>
       <c r="P5" t="n">
-        <v>319.9193645492463</v>
+        <v>319.8951097981201</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26222,28 +26271,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1969790825398256</v>
+        <v>-0.1949572395598667</v>
       </c>
       <c r="J6" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K6" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07754027323401969</v>
+        <v>0.07622477086629709</v>
       </c>
       <c r="M6" t="n">
-        <v>4.172275944546541</v>
+        <v>4.172984654354702</v>
       </c>
       <c r="N6" t="n">
-        <v>25.74137021279775</v>
+        <v>25.7448022765003</v>
       </c>
       <c r="O6" t="n">
-        <v>5.073595393091348</v>
+        <v>5.073933609784454</v>
       </c>
       <c r="P6" t="n">
-        <v>317.0158993424091</v>
+        <v>316.9948486409028</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26300,28 +26349,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0440429898895334</v>
+        <v>-0.04218710182526732</v>
       </c>
       <c r="J7" t="n">
+        <v>511</v>
+      </c>
+      <c r="K7" t="n">
         <v>510</v>
       </c>
-      <c r="K7" t="n">
-        <v>509</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001482180643971209</v>
+        <v>0.00136494515159391</v>
       </c>
       <c r="M7" t="n">
-        <v>6.729250261827961</v>
+        <v>6.723602913336264</v>
       </c>
       <c r="N7" t="n">
-        <v>72.46693922909331</v>
+        <v>72.37019438000476</v>
       </c>
       <c r="O7" t="n">
-        <v>8.512751566273581</v>
+        <v>8.507067319588153</v>
       </c>
       <c r="P7" t="n">
-        <v>304.8396490852739</v>
+        <v>304.8202828813863</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26378,28 +26427,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05935052412634512</v>
+        <v>0.06129623723074229</v>
       </c>
       <c r="J8" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K8" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003692562878333749</v>
+        <v>0.003950489778831723</v>
       </c>
       <c r="M8" t="n">
-        <v>5.886124979859833</v>
+        <v>5.882104669827751</v>
       </c>
       <c r="N8" t="n">
-        <v>52.80213325105596</v>
+        <v>52.7483580873079</v>
       </c>
       <c r="O8" t="n">
-        <v>7.266507637858503</v>
+        <v>7.26280648835613</v>
       </c>
       <c r="P8" t="n">
-        <v>299.5408296848299</v>
+        <v>299.5205408382596</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26456,28 +26505,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01059611808539598</v>
+        <v>0.01453794268387848</v>
       </c>
       <c r="J9" t="n">
+        <v>511</v>
+      </c>
+      <c r="K9" t="n">
         <v>510</v>
       </c>
-      <c r="K9" t="n">
-        <v>509</v>
-      </c>
       <c r="L9" t="n">
-        <v>5.072050063181788e-05</v>
+        <v>9.571724361567835e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>9.338236736469874</v>
+        <v>9.336786138718027</v>
       </c>
       <c r="N9" t="n">
-        <v>121.7157782978529</v>
+        <v>121.6792571167374</v>
       </c>
       <c r="O9" t="n">
-        <v>11.03248740302263</v>
+        <v>11.03083211352332</v>
       </c>
       <c r="P9" t="n">
-        <v>297.077576620649</v>
+        <v>297.0362180279457</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26534,28 +26583,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.140643703435111</v>
+        <v>0.1410091794717839</v>
       </c>
       <c r="J10" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05013570922671839</v>
+        <v>0.0505814382157006</v>
       </c>
       <c r="M10" t="n">
-        <v>3.560217889467531</v>
+        <v>3.555092949887359</v>
       </c>
       <c r="N10" t="n">
-        <v>20.74359082617702</v>
+        <v>20.70475112957159</v>
       </c>
       <c r="O10" t="n">
-        <v>4.554513237018531</v>
+        <v>4.550247370151604</v>
       </c>
       <c r="P10" t="n">
-        <v>302.2670792117113</v>
+        <v>302.2632627334979</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26593,7 +26642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K511"/>
+  <dimension ref="A1:K512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55683,6 +55732,63 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:21:27+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>-46.59079351008663,168.80597441252888</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>-46.59017742297976,168.8060606392916</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>-46.58953022501109,168.80580763360737</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-46.58894110463762,168.80543691579004</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-46.58839760147977,168.80495535045387</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>-46.58789049673936,168.8043831420945</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-46.58745006080025,168.80373484009434</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-46.587043228357956,168.80303234707173</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-46.586662478827556,168.80230646124048</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K512"/>
+  <dimension ref="A1:K514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20394,6 +20394,84 @@
       <c r="K512" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>315.16</v>
+      </c>
+      <c r="C513" t="n">
+        <v>309.57</v>
+      </c>
+      <c r="D513" t="n">
+        <v>333.25</v>
+      </c>
+      <c r="E513" t="n">
+        <v>321.04</v>
+      </c>
+      <c r="F513" t="n">
+        <v>320.02</v>
+      </c>
+      <c r="G513" t="n">
+        <v>312.64</v>
+      </c>
+      <c r="H513" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="I513" t="n">
+        <v>314.39</v>
+      </c>
+      <c r="J513" t="n">
+        <v>307.28</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>320.02</v>
+      </c>
+      <c r="C514" t="n">
+        <v>313.59</v>
+      </c>
+      <c r="D514" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="E514" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="F514" t="n">
+        <v>323.76</v>
+      </c>
+      <c r="G514" t="n">
+        <v>316.55</v>
+      </c>
+      <c r="H514" t="n">
+        <v>313.54</v>
+      </c>
+      <c r="I514" t="n">
+        <v>313.9</v>
+      </c>
+      <c r="J514" t="n">
+        <v>309.84</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20408,7 +20486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B538"/>
+  <dimension ref="A1:B540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25791,6 +25869,26 @@
       </c>
       <c r="B538" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -25959,28 +26057,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4218898824437722</v>
+        <v>-0.4159129357103849</v>
       </c>
       <c r="J2" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K2" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2089492168190843</v>
+        <v>0.2045619051403657</v>
       </c>
       <c r="M2" t="n">
-        <v>4.316307246768432</v>
+        <v>4.321566098922562</v>
       </c>
       <c r="N2" t="n">
-        <v>37.13677942925308</v>
+        <v>37.24408035651</v>
       </c>
       <c r="O2" t="n">
-        <v>6.093995358486342</v>
+        <v>6.102792832507916</v>
       </c>
       <c r="P2" t="n">
-        <v>321.1019768683092</v>
+        <v>321.0388328481953</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26037,28 +26135,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1687139043417997</v>
+        <v>-0.164758626958412</v>
       </c>
       <c r="J3" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K3" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06358846439958221</v>
+        <v>0.06102229412817572</v>
       </c>
       <c r="M3" t="n">
-        <v>3.77398876225385</v>
+        <v>3.778912664136716</v>
       </c>
       <c r="N3" t="n">
-        <v>23.25406429366144</v>
+        <v>23.28049506544108</v>
       </c>
       <c r="O3" t="n">
-        <v>4.822246809699959</v>
+        <v>4.824986535260081</v>
       </c>
       <c r="P3" t="n">
-        <v>310.9344736749738</v>
+        <v>310.8928812610478</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26115,28 +26213,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2438192758693317</v>
+        <v>-0.234726131152345</v>
       </c>
       <c r="J4" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K4" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1148163936894608</v>
+        <v>0.1060317817831935</v>
       </c>
       <c r="M4" t="n">
-        <v>4.032205419813741</v>
+        <v>4.061538044393473</v>
       </c>
       <c r="N4" t="n">
-        <v>25.4257770116725</v>
+        <v>25.89035673002554</v>
       </c>
       <c r="O4" t="n">
-        <v>5.042397942613465</v>
+        <v>5.088256747651944</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6129963003463</v>
+        <v>330.5173908387751</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26193,28 +26291,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2713332342204811</v>
+        <v>-0.2629622466886719</v>
       </c>
       <c r="J5" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K5" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1333904886813705</v>
+        <v>0.1252759837442915</v>
       </c>
       <c r="M5" t="n">
-        <v>4.067082467766141</v>
+        <v>4.09380439484698</v>
       </c>
       <c r="N5" t="n">
-        <v>26.56826457884221</v>
+        <v>26.94402598495773</v>
       </c>
       <c r="O5" t="n">
-        <v>5.154441247976566</v>
+        <v>5.190763526202839</v>
       </c>
       <c r="P5" t="n">
-        <v>319.8951097981201</v>
+        <v>319.8071103083682</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26271,28 +26369,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1949572395598667</v>
+        <v>-0.1871959314486435</v>
       </c>
       <c r="J6" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K6" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07622477086629709</v>
+        <v>0.07022308361081819</v>
       </c>
       <c r="M6" t="n">
-        <v>4.172984654354702</v>
+        <v>4.190253473240745</v>
       </c>
       <c r="N6" t="n">
-        <v>25.7448022765003</v>
+        <v>26.05144396783657</v>
       </c>
       <c r="O6" t="n">
-        <v>5.073933609784454</v>
+        <v>5.104061516854648</v>
       </c>
       <c r="P6" t="n">
-        <v>316.9948486409028</v>
+        <v>316.9134832761761</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26349,28 +26447,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04218710182526732</v>
+        <v>-0.03378829255143374</v>
       </c>
       <c r="J7" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K7" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00136494515159391</v>
+        <v>0.0008777568201441266</v>
       </c>
       <c r="M7" t="n">
-        <v>6.723602913336264</v>
+        <v>6.731476079049792</v>
       </c>
       <c r="N7" t="n">
-        <v>72.37019438000476</v>
+        <v>72.56058744099818</v>
       </c>
       <c r="O7" t="n">
-        <v>8.507067319588153</v>
+        <v>8.518250257006903</v>
       </c>
       <c r="P7" t="n">
-        <v>304.8202828813863</v>
+        <v>304.7320430489479</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26427,28 +26525,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06129623723074229</v>
+        <v>0.06949744452458592</v>
       </c>
       <c r="J8" t="n">
+        <v>513</v>
+      </c>
+      <c r="K8" t="n">
         <v>511</v>
       </c>
-      <c r="K8" t="n">
-        <v>509</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.003950489778831723</v>
+        <v>0.005072735746808998</v>
       </c>
       <c r="M8" t="n">
-        <v>5.882104669827751</v>
+        <v>5.890407720427794</v>
       </c>
       <c r="N8" t="n">
-        <v>52.7483580873079</v>
+        <v>52.99170869563331</v>
       </c>
       <c r="O8" t="n">
-        <v>7.26280648835613</v>
+        <v>7.279540417885824</v>
       </c>
       <c r="P8" t="n">
-        <v>299.5205408382596</v>
+        <v>299.4344387855629</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26505,28 +26603,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01453794268387848</v>
+        <v>0.0274972427744188</v>
       </c>
       <c r="J9" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K9" t="n">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L9" t="n">
-        <v>9.571724361567835e-05</v>
+        <v>0.0003422432232443873</v>
       </c>
       <c r="M9" t="n">
-        <v>9.336786138718027</v>
+        <v>9.35523450683427</v>
       </c>
       <c r="N9" t="n">
-        <v>121.6792571167374</v>
+        <v>122.2828498250995</v>
       </c>
       <c r="O9" t="n">
-        <v>11.03083211352332</v>
+        <v>11.05815761440845</v>
       </c>
       <c r="P9" t="n">
-        <v>297.0362180279457</v>
+        <v>296.8993513737017</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26583,28 +26681,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1410091794717839</v>
+        <v>0.1429747915518273</v>
       </c>
       <c r="J10" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="K10" t="n">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0505814382157006</v>
+        <v>0.05227532212393315</v>
       </c>
       <c r="M10" t="n">
-        <v>3.555092949887359</v>
+        <v>3.550951328018868</v>
       </c>
       <c r="N10" t="n">
-        <v>20.70475112957159</v>
+        <v>20.65539712138312</v>
       </c>
       <c r="O10" t="n">
-        <v>4.550247370151604</v>
+        <v>4.544820911915355</v>
       </c>
       <c r="P10" t="n">
-        <v>302.2632627334979</v>
+        <v>302.242590847823</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26642,7 +26740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K512"/>
+  <dimension ref="A1:K514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55789,6 +55887,120 @@
         </is>
       </c>
     </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>-46.590792136631485,168.80594932897876</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>-46.59017741655148,168.80606050925107</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>-46.58953659259572,168.8057688234445</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-46.588951642357884,168.8054108160061</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-46.58841334268314,168.8049244023346</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-46.58791625601592,168.80434419290438</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>-46.587475081158544,168.80369960434317</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-46.58708955429733,168.80297352774872</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-46.586664854056096,168.80230367242274</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>-46.5907886780622,168.80588616522778</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>-46.59017483237475,168.80600823296024</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>-46.58954772543182,168.80570096905495</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-46.588974352940454,168.80535456643815</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-46.588433299314424,168.8048851663884</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>-46.587940584208155,168.80430740752425</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>-46.58749758657363,168.80366791030207</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-46.58708624047213,168.8029777352657</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-46.5866827381274,168.80228267425775</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K514"/>
+  <dimension ref="A1:K516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20470,6 +20470,84 @@
         <v>309.84</v>
       </c>
       <c r="K514" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>320.74</v>
+      </c>
+      <c r="C515" t="n">
+        <v>314.82</v>
+      </c>
+      <c r="D515" t="n">
+        <v>338.65</v>
+      </c>
+      <c r="E515" t="n">
+        <v>326.54</v>
+      </c>
+      <c r="F515" t="n">
+        <v>323.93</v>
+      </c>
+      <c r="G515" t="n">
+        <v>317.1</v>
+      </c>
+      <c r="H515" t="n">
+        <v>313.74</v>
+      </c>
+      <c r="I515" t="n">
+        <v>313.81</v>
+      </c>
+      <c r="J515" t="n">
+        <v>310.18</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>321.1</v>
+      </c>
+      <c r="C516" t="n">
+        <v>314.53</v>
+      </c>
+      <c r="D516" t="n">
+        <v>337.98</v>
+      </c>
+      <c r="E516" t="n">
+        <v>326.17</v>
+      </c>
+      <c r="F516" t="n">
+        <v>323.37</v>
+      </c>
+      <c r="G516" t="n">
+        <v>317.28</v>
+      </c>
+      <c r="H516" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="I516" t="n">
+        <v>313.43</v>
+      </c>
+      <c r="J516" t="n">
+        <v>310.15</v>
+      </c>
+      <c r="K516" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20486,7 +20564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B540"/>
+  <dimension ref="A1:B542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25889,6 +25967,26 @@
       </c>
       <c r="B540" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>-1.12</v>
       </c>
     </row>
   </sheetData>
@@ -26057,28 +26155,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4159129357103849</v>
+        <v>-0.407465799827745</v>
       </c>
       <c r="J2" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K2" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2045619051403657</v>
+        <v>0.1973563162068644</v>
       </c>
       <c r="M2" t="n">
-        <v>4.321566098922562</v>
+        <v>4.336833025150859</v>
       </c>
       <c r="N2" t="n">
-        <v>37.24408035651</v>
+        <v>37.56161178745086</v>
       </c>
       <c r="O2" t="n">
-        <v>6.102792832507916</v>
+        <v>6.128752873746082</v>
       </c>
       <c r="P2" t="n">
-        <v>321.0388328481953</v>
+        <v>320.9493592091752</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26135,28 +26233,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.164758626958412</v>
+        <v>-0.1585007706934572</v>
       </c>
       <c r="J3" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K3" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06102229412817572</v>
+        <v>0.05660087713536965</v>
       </c>
       <c r="M3" t="n">
-        <v>3.778912664136716</v>
+        <v>3.795576345480398</v>
       </c>
       <c r="N3" t="n">
-        <v>23.28049506544108</v>
+        <v>23.44637286421882</v>
       </c>
       <c r="O3" t="n">
-        <v>4.824986535260081</v>
+        <v>4.842145481521473</v>
       </c>
       <c r="P3" t="n">
-        <v>310.8928812610478</v>
+        <v>310.8269098929277</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26213,28 +26311,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.234726131152345</v>
+        <v>-0.2239676637508767</v>
       </c>
       <c r="J4" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K4" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1060317817831935</v>
+        <v>0.09567764364931519</v>
       </c>
       <c r="M4" t="n">
-        <v>4.061538044393473</v>
+        <v>4.09888004645782</v>
       </c>
       <c r="N4" t="n">
-        <v>25.89035673002554</v>
+        <v>26.54752510220264</v>
       </c>
       <c r="O4" t="n">
-        <v>5.088256747651944</v>
+        <v>5.152429048730574</v>
       </c>
       <c r="P4" t="n">
-        <v>330.5173908387751</v>
+        <v>330.4039740214673</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26291,28 +26389,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2629622466886719</v>
+        <v>-0.2525847555897959</v>
       </c>
       <c r="J5" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K5" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1252759837442915</v>
+        <v>0.1149269965758184</v>
       </c>
       <c r="M5" t="n">
-        <v>4.09380439484698</v>
+        <v>4.13088984577875</v>
       </c>
       <c r="N5" t="n">
-        <v>26.94402598495773</v>
+        <v>27.54537491896599</v>
       </c>
       <c r="O5" t="n">
-        <v>5.190763526202839</v>
+        <v>5.24836878648652</v>
       </c>
       <c r="P5" t="n">
-        <v>319.8071103083682</v>
+        <v>319.6977245528171</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26369,28 +26467,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1871959314486435</v>
+        <v>-0.178223905839002</v>
       </c>
       <c r="J6" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K6" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07022308361081819</v>
+        <v>0.06337073276438043</v>
       </c>
       <c r="M6" t="n">
-        <v>4.190253473240745</v>
+        <v>4.212478498503373</v>
       </c>
       <c r="N6" t="n">
-        <v>26.05144396783657</v>
+        <v>26.48143931892505</v>
       </c>
       <c r="O6" t="n">
-        <v>5.104061516854648</v>
+        <v>5.146011982003642</v>
       </c>
       <c r="P6" t="n">
-        <v>316.9134832761761</v>
+        <v>316.8191671519047</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26447,28 +26545,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03378829255143374</v>
+        <v>-0.02356039174540748</v>
       </c>
       <c r="J7" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008777568201441266</v>
+        <v>0.0004265791991807655</v>
       </c>
       <c r="M7" t="n">
-        <v>6.731476079049792</v>
+        <v>6.746676963860644</v>
       </c>
       <c r="N7" t="n">
-        <v>72.56058744099818</v>
+        <v>72.96424659572608</v>
       </c>
       <c r="O7" t="n">
-        <v>8.518250257006903</v>
+        <v>8.541911179339555</v>
       </c>
       <c r="P7" t="n">
-        <v>304.7320430489479</v>
+        <v>304.624290157184</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26525,28 +26623,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06949744452458592</v>
+        <v>0.07898162969009982</v>
       </c>
       <c r="J8" t="n">
+        <v>515</v>
+      </c>
+      <c r="K8" t="n">
         <v>513</v>
       </c>
-      <c r="K8" t="n">
-        <v>511</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.005072735746808998</v>
+        <v>0.006525022024484239</v>
       </c>
       <c r="M8" t="n">
-        <v>5.890407720427794</v>
+        <v>5.905355568310775</v>
       </c>
       <c r="N8" t="n">
-        <v>52.99170869563331</v>
+        <v>53.37638730444939</v>
       </c>
       <c r="O8" t="n">
-        <v>7.279540417885824</v>
+        <v>7.30591454264621</v>
       </c>
       <c r="P8" t="n">
-        <v>299.4344387855629</v>
+        <v>299.3345914754879</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26603,28 +26701,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0274972427744188</v>
+        <v>0.03981098486260141</v>
       </c>
       <c r="J9" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K9" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0003422432232443873</v>
+        <v>0.0007175005100427123</v>
       </c>
       <c r="M9" t="n">
-        <v>9.35523450683427</v>
+        <v>9.371026082518259</v>
       </c>
       <c r="N9" t="n">
-        <v>122.2828498250995</v>
+        <v>122.7897295390187</v>
       </c>
       <c r="O9" t="n">
-        <v>11.05815761440845</v>
+        <v>11.08105272702096</v>
       </c>
       <c r="P9" t="n">
-        <v>296.8993513737017</v>
+        <v>296.7689257335102</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26681,28 +26779,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1429747915518273</v>
+        <v>0.1461246346988073</v>
       </c>
       <c r="J10" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K10" t="n">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05227532212393315</v>
+        <v>0.05475457676547779</v>
       </c>
       <c r="M10" t="n">
-        <v>3.550951328018868</v>
+        <v>3.552630515765045</v>
       </c>
       <c r="N10" t="n">
-        <v>20.65539712138312</v>
+        <v>20.6400924302292</v>
       </c>
       <c r="O10" t="n">
-        <v>4.544820911915355</v>
+        <v>4.543136849163713</v>
       </c>
       <c r="P10" t="n">
-        <v>302.242590847823</v>
+        <v>302.2093842673782</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26740,7 +26838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K514"/>
+  <dimension ref="A1:K516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56001,6 +56099,120 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>-46.59078816567861,168.8058768076359</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>-46.59017404168906,168.80599223797705</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>-46.58954782947682,168.80570033490167</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-46.588976623997084,168.80534894147885</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>-46.588434206433696,168.80488338293563</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>-46.58794400633135,168.80430223310756</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-46.58749887628195,168.8036660940238</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-46.587085631810346,168.80297850807486</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-46.58668511335528,168.8022798854379</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:42+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>-46.590787909486544,168.80587212884006</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>-46.590174228111096,168.8059960091519</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>-46.58954643527349,168.80570883255558</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-46.5889749434152,168.8053531039488</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>-46.588431218276014,168.80488925783865</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>-46.58794512629887,168.80430053966194</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-46.58749810245697,168.80366718379076</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-46.587083061904956,168.80298177104677</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-46.58668490377636,168.8022801315103</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20548,6 +20548,45 @@
         <v>310.15</v>
       </c>
       <c r="K516" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>319.69</v>
+      </c>
+      <c r="C517" t="n">
+        <v>313.71</v>
+      </c>
+      <c r="D517" t="n">
+        <v>336.81</v>
+      </c>
+      <c r="E517" t="n">
+        <v>325</v>
+      </c>
+      <c r="F517" t="n">
+        <v>322.16</v>
+      </c>
+      <c r="G517" t="n">
+        <v>316.52</v>
+      </c>
+      <c r="H517" t="n">
+        <v>313</v>
+      </c>
+      <c r="I517" t="n">
+        <v>313.19</v>
+      </c>
+      <c r="J517" t="n">
+        <v>309.4</v>
+      </c>
+      <c r="K517" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -20564,7 +20603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B542"/>
+  <dimension ref="A1:B543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25987,6 +26026,16 @@
       </c>
       <c r="B542" t="n">
         <v>-1.12</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -26155,28 +26204,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.407465799827745</v>
+        <v>-0.4037489698902259</v>
       </c>
       <c r="J2" t="n">
+        <v>516</v>
+      </c>
+      <c r="K2" t="n">
         <v>515</v>
       </c>
-      <c r="K2" t="n">
-        <v>514</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1973563162068644</v>
+        <v>0.1943938825445474</v>
       </c>
       <c r="M2" t="n">
-        <v>4.336833025150859</v>
+        <v>4.342365746989045</v>
       </c>
       <c r="N2" t="n">
-        <v>37.56161178745086</v>
+        <v>37.6679089786771</v>
       </c>
       <c r="O2" t="n">
-        <v>6.128752873746082</v>
+        <v>6.13741875536264</v>
       </c>
       <c r="P2" t="n">
-        <v>320.9493592091752</v>
+        <v>320.9098445668412</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26233,28 +26282,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1585007706934572</v>
+        <v>-0.1557685071194099</v>
       </c>
       <c r="J3" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K3" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05660087713536965</v>
+        <v>0.0547777270395774</v>
       </c>
       <c r="M3" t="n">
-        <v>3.795576345480398</v>
+        <v>3.801966830876296</v>
       </c>
       <c r="N3" t="n">
-        <v>23.44637286421882</v>
+        <v>23.49872111685149</v>
       </c>
       <c r="O3" t="n">
-        <v>4.842145481521473</v>
+        <v>4.847547948896585</v>
       </c>
       <c r="P3" t="n">
-        <v>310.8269098929277</v>
+        <v>310.7979980020954</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26311,28 +26360,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2239676637508767</v>
+        <v>-0.2192143669298477</v>
       </c>
       <c r="J4" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K4" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09567764364931519</v>
+        <v>0.09146004064374236</v>
       </c>
       <c r="M4" t="n">
-        <v>4.09888004645782</v>
+        <v>4.114362000195715</v>
       </c>
       <c r="N4" t="n">
-        <v>26.54752510220264</v>
+        <v>26.79203137428038</v>
       </c>
       <c r="O4" t="n">
-        <v>5.152429048730574</v>
+        <v>5.176101947825253</v>
       </c>
       <c r="P4" t="n">
-        <v>330.4039740214673</v>
+        <v>330.3536762390395</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26389,28 +26438,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2525847555897959</v>
+        <v>-0.2479607866821767</v>
       </c>
       <c r="J5" t="n">
+        <v>516</v>
+      </c>
+      <c r="K5" t="n">
         <v>515</v>
       </c>
-      <c r="K5" t="n">
-        <v>514</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1149269965758184</v>
+        <v>0.110640952799462</v>
       </c>
       <c r="M5" t="n">
-        <v>4.13088984577875</v>
+        <v>4.146445321560541</v>
       </c>
       <c r="N5" t="n">
-        <v>27.54537491896599</v>
+        <v>27.77254775048091</v>
       </c>
       <c r="O5" t="n">
-        <v>5.24836878648652</v>
+        <v>5.269966579636052</v>
       </c>
       <c r="P5" t="n">
-        <v>319.6977245528171</v>
+        <v>319.6488018590247</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26467,28 +26516,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.178223905839002</v>
+        <v>-0.1743520744933893</v>
       </c>
       <c r="J6" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K6" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06337073276438043</v>
+        <v>0.06063004548871043</v>
       </c>
       <c r="M6" t="n">
-        <v>4.212478498503373</v>
+        <v>4.220825135790818</v>
       </c>
       <c r="N6" t="n">
-        <v>26.48143931892505</v>
+        <v>26.6279416875997</v>
       </c>
       <c r="O6" t="n">
-        <v>5.146011982003642</v>
+        <v>5.160226902724308</v>
       </c>
       <c r="P6" t="n">
-        <v>316.8191671519047</v>
+        <v>316.7783108111214</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26545,28 +26594,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02356039174540748</v>
+        <v>-0.01875726446366823</v>
       </c>
       <c r="J7" t="n">
+        <v>516</v>
+      </c>
+      <c r="K7" t="n">
         <v>515</v>
       </c>
-      <c r="K7" t="n">
-        <v>514</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0004265791991807655</v>
+        <v>0.000270454757386962</v>
       </c>
       <c r="M7" t="n">
-        <v>6.746676963860644</v>
+        <v>6.753317193765439</v>
       </c>
       <c r="N7" t="n">
-        <v>72.96424659572608</v>
+        <v>73.12547371658113</v>
       </c>
       <c r="O7" t="n">
-        <v>8.541911179339555</v>
+        <v>8.551343386660433</v>
       </c>
       <c r="P7" t="n">
-        <v>304.624290157184</v>
+        <v>304.5734993427265</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26623,28 +26672,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07898162969009982</v>
+        <v>0.08341106993899014</v>
       </c>
       <c r="J8" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K8" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006525022024484239</v>
+        <v>0.007267870810367505</v>
       </c>
       <c r="M8" t="n">
-        <v>5.905355568310775</v>
+        <v>5.911770026450101</v>
       </c>
       <c r="N8" t="n">
-        <v>53.37638730444939</v>
+        <v>53.53075686747341</v>
       </c>
       <c r="O8" t="n">
-        <v>7.30591454264621</v>
+        <v>7.316471613248658</v>
       </c>
       <c r="P8" t="n">
-        <v>299.3345914754879</v>
+        <v>299.2877841088626</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26701,28 +26750,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03981098486260141</v>
+        <v>0.04573302953594194</v>
       </c>
       <c r="J9" t="n">
+        <v>516</v>
+      </c>
+      <c r="K9" t="n">
         <v>515</v>
       </c>
-      <c r="K9" t="n">
-        <v>514</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.0007175005100427123</v>
+        <v>0.0009471734499293394</v>
       </c>
       <c r="M9" t="n">
-        <v>9.371026082518259</v>
+        <v>9.377973097626731</v>
       </c>
       <c r="N9" t="n">
-        <v>122.7897295390187</v>
+        <v>123.0063060262709</v>
       </c>
       <c r="O9" t="n">
-        <v>11.08105272702096</v>
+        <v>11.09082080038583</v>
       </c>
       <c r="P9" t="n">
-        <v>296.7689257335102</v>
+        <v>296.7059668462093</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26779,28 +26828,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1461246346988073</v>
+        <v>0.1473839414200238</v>
       </c>
       <c r="J10" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K10" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05475457676547779</v>
+        <v>0.05582162453326101</v>
       </c>
       <c r="M10" t="n">
-        <v>3.552630515765045</v>
+        <v>3.551950649917721</v>
       </c>
       <c r="N10" t="n">
-        <v>20.6400924302292</v>
+        <v>20.62086523105095</v>
       </c>
       <c r="O10" t="n">
-        <v>4.543136849163713</v>
+        <v>4.541020285249886</v>
       </c>
       <c r="P10" t="n">
-        <v>302.2093842673782</v>
+        <v>302.1960587087484</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26838,7 +26887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K516"/>
+  <dimension ref="A1:K517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56213,6 +56262,63 @@
         </is>
       </c>
     </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>-46.59078891290443,168.80589045412412</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>-46.59017475523477,168.80600667247404</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>-46.58954400061836,168.8057236717414</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-46.58896962914169,168.80536626635208</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-46.58842476171993,168.8049019518234</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>-46.587940397546895,168.80430768976515</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-46.58749410436105,168.80367281425282</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-46.587081438806756,168.802983831871</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-46.58667966430296,168.80228628331835</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K517"/>
+  <dimension ref="A1:K521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20589,6 +20589,162 @@
       <c r="K517" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>320.37</v>
+      </c>
+      <c r="C518" t="n">
+        <v>313.94</v>
+      </c>
+      <c r="D518" t="n">
+        <v>336.44</v>
+      </c>
+      <c r="E518" t="n">
+        <v>324.83</v>
+      </c>
+      <c r="F518" t="n">
+        <v>322.27</v>
+      </c>
+      <c r="G518" t="n">
+        <v>317.01</v>
+      </c>
+      <c r="H518" t="n">
+        <v>313.69</v>
+      </c>
+      <c r="I518" t="n">
+        <v>313.28</v>
+      </c>
+      <c r="J518" t="n">
+        <v>309.21</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="C519" t="n">
+        <v>312.88</v>
+      </c>
+      <c r="D519" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="E519" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="F519" t="n">
+        <v>321.2</v>
+      </c>
+      <c r="G519" t="n">
+        <v>316.02</v>
+      </c>
+      <c r="H519" t="n">
+        <v>312.48</v>
+      </c>
+      <c r="I519" t="n">
+        <v>311.99</v>
+      </c>
+      <c r="J519" t="n">
+        <v>309.33</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>319.92</v>
+      </c>
+      <c r="C520" t="n">
+        <v>312.92</v>
+      </c>
+      <c r="D520" t="n">
+        <v>335.97</v>
+      </c>
+      <c r="E520" t="n">
+        <v>323.86</v>
+      </c>
+      <c r="F520" t="n">
+        <v>321.58</v>
+      </c>
+      <c r="G520" t="n">
+        <v>315.99</v>
+      </c>
+      <c r="H520" t="n">
+        <v>311.88</v>
+      </c>
+      <c r="I520" t="n">
+        <v>309.31</v>
+      </c>
+      <c r="J520" t="n">
+        <v>309.68</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>320.76</v>
+      </c>
+      <c r="C521" t="n">
+        <v>313.75</v>
+      </c>
+      <c r="D521" t="n">
+        <v>336.42</v>
+      </c>
+      <c r="E521" t="n">
+        <v>324.22</v>
+      </c>
+      <c r="F521" t="n">
+        <v>321.87</v>
+      </c>
+      <c r="G521" t="n">
+        <v>315.95</v>
+      </c>
+      <c r="H521" t="n">
+        <v>311.81</v>
+      </c>
+      <c r="I521" t="n">
+        <v>309.76</v>
+      </c>
+      <c r="J521" t="n">
+        <v>309.35</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20603,7 +20759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B543"/>
+  <dimension ref="A1:B547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26036,6 +26192,46 @@
       </c>
       <c r="B543" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -26204,28 +26400,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4037489698902259</v>
+        <v>-0.3884376134504392</v>
       </c>
       <c r="J2" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K2" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1943938825445474</v>
+        <v>0.1820609427659134</v>
       </c>
       <c r="M2" t="n">
-        <v>4.342365746989045</v>
+        <v>4.372226784219206</v>
       </c>
       <c r="N2" t="n">
-        <v>37.6679089786771</v>
+        <v>38.14841555939795</v>
       </c>
       <c r="O2" t="n">
-        <v>6.13741875536264</v>
+        <v>6.176440363137813</v>
       </c>
       <c r="P2" t="n">
-        <v>320.9098445668412</v>
+        <v>320.7466371704064</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26282,28 +26478,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1557685071194099</v>
+        <v>-0.1456127009454706</v>
       </c>
       <c r="J3" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K3" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0547777270395774</v>
+        <v>0.04830715628694082</v>
       </c>
       <c r="M3" t="n">
-        <v>3.801966830876296</v>
+        <v>3.823987472322107</v>
       </c>
       <c r="N3" t="n">
-        <v>23.49872111685149</v>
+        <v>23.66161742946548</v>
       </c>
       <c r="O3" t="n">
-        <v>4.847547948896585</v>
+        <v>4.864320860044645</v>
       </c>
       <c r="P3" t="n">
-        <v>310.7979980020954</v>
+        <v>310.6902522218776</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26360,28 +26556,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2192143669298477</v>
+        <v>-0.2017034692471131</v>
       </c>
       <c r="J4" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K4" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09146004064374236</v>
+        <v>0.07705562295079871</v>
       </c>
       <c r="M4" t="n">
-        <v>4.114362000195715</v>
+        <v>4.168345196525939</v>
       </c>
       <c r="N4" t="n">
-        <v>26.79203137428038</v>
+        <v>27.60314141479029</v>
       </c>
       <c r="O4" t="n">
-        <v>5.176101947825253</v>
+        <v>5.25386918516157</v>
       </c>
       <c r="P4" t="n">
-        <v>330.3536762390395</v>
+        <v>330.1678936287211</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26438,28 +26634,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2479607866821767</v>
+        <v>-0.231203006074205</v>
       </c>
       <c r="J5" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K5" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L5" t="n">
-        <v>0.110640952799462</v>
+        <v>0.09616585927256593</v>
       </c>
       <c r="M5" t="n">
-        <v>4.146445321560541</v>
+        <v>4.199185113640731</v>
       </c>
       <c r="N5" t="n">
-        <v>27.77254775048091</v>
+        <v>28.49285487680254</v>
       </c>
       <c r="O5" t="n">
-        <v>5.269966579636052</v>
+        <v>5.337869881966264</v>
       </c>
       <c r="P5" t="n">
-        <v>319.6488018590247</v>
+        <v>319.4710361935439</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26516,28 +26712,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1743520744933893</v>
+        <v>-0.1598832352132466</v>
       </c>
       <c r="J6" t="n">
+        <v>520</v>
+      </c>
+      <c r="K6" t="n">
         <v>516</v>
       </c>
-      <c r="K6" t="n">
-        <v>512</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.06063004548871043</v>
+        <v>0.0510289563079187</v>
       </c>
       <c r="M6" t="n">
-        <v>4.220825135790818</v>
+        <v>4.252599312844065</v>
       </c>
       <c r="N6" t="n">
-        <v>26.6279416875997</v>
+        <v>27.12318023091392</v>
       </c>
       <c r="O6" t="n">
-        <v>5.160226902724308</v>
+        <v>5.207991957646817</v>
       </c>
       <c r="P6" t="n">
-        <v>316.7783108111214</v>
+        <v>316.6252274973741</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26594,28 +26790,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01875726446366823</v>
+        <v>-0.0004441830295382435</v>
       </c>
       <c r="J7" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K7" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000270454757386962</v>
+        <v>1.519581677156268e-07</v>
       </c>
       <c r="M7" t="n">
-        <v>6.753317193765439</v>
+        <v>6.777334014337643</v>
       </c>
       <c r="N7" t="n">
-        <v>73.12547371658113</v>
+        <v>73.67780184323954</v>
       </c>
       <c r="O7" t="n">
-        <v>8.551343386660433</v>
+        <v>8.583577450180055</v>
       </c>
       <c r="P7" t="n">
-        <v>304.5734993427265</v>
+        <v>304.3793425705257</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26672,28 +26868,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08341106993899014</v>
+        <v>0.09986451155885552</v>
       </c>
       <c r="J8" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K8" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L8" t="n">
-        <v>0.007267870810367505</v>
+        <v>0.01038532755184396</v>
       </c>
       <c r="M8" t="n">
-        <v>5.911770026450101</v>
+        <v>5.931992366752588</v>
       </c>
       <c r="N8" t="n">
-        <v>53.53075686747341</v>
+        <v>54.02364989811114</v>
       </c>
       <c r="O8" t="n">
-        <v>7.316471613248658</v>
+        <v>7.350078223945045</v>
       </c>
       <c r="P8" t="n">
-        <v>299.2877841088626</v>
+        <v>299.1134686023512</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26750,28 +26946,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04573302953594194</v>
+        <v>0.06562996023191631</v>
       </c>
       <c r="J9" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K9" t="n">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009471734499293394</v>
+        <v>0.001960829323573998</v>
       </c>
       <c r="M9" t="n">
-        <v>9.377973097626731</v>
+        <v>9.390295875471551</v>
       </c>
       <c r="N9" t="n">
-        <v>123.0063060262709</v>
+        <v>123.3791764625062</v>
       </c>
       <c r="O9" t="n">
-        <v>11.09082080038583</v>
+        <v>11.10761794726962</v>
       </c>
       <c r="P9" t="n">
-        <v>296.7059668462093</v>
+        <v>296.4939152246554</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26828,28 +27024,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1473839414200238</v>
+        <v>0.1522690775308647</v>
       </c>
       <c r="J10" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="K10" t="n">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05582162453326101</v>
+        <v>0.06009452979826413</v>
       </c>
       <c r="M10" t="n">
-        <v>3.551950649917721</v>
+        <v>3.548378832993331</v>
       </c>
       <c r="N10" t="n">
-        <v>20.62086523105095</v>
+        <v>20.5415518961501</v>
       </c>
       <c r="O10" t="n">
-        <v>4.541020285249886</v>
+        <v>4.532278885522172</v>
       </c>
       <c r="P10" t="n">
-        <v>302.1960587087484</v>
+        <v>302.1442272242189</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26887,7 +27083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K517"/>
+  <dimension ref="A1:K521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56319,6 +56515,234 @@
         </is>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>-46.590788428986954,168.80588161639838</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>-46.59017460738311,168.8060036815422</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>-46.58954323068427,168.8057283644751</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-46.588968856982156,168.8053681788378</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>-46.588425348679635,168.8049007978249</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>-46.58794344634758,168.80430307983033</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-46.58749855385487,168.8036665480934</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-46.587082047468584,168.80298305906194</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-46.58667833696963,168.8022878417762</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>-46.590788855973,168.80588941439166</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>-46.59017528878581,168.806017465837</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>-46.58954156596126,168.80573851092592</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-46.58896349728565,168.80538145373734</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>-46.588419639161955,168.80491202308193</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>-46.58793728652558,168.80431239377978</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-46.587490751119084,168.80367753657518</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-46.58707332331514,168.8029941359902</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-46.58667917528542,168.80228685748705</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>-46.59078874922653,168.80588746489332</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>-46.590175263072524,168.8060169456749</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>-46.58954225265961,168.80573432551503</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-46.58896445113005,168.80537909125542</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>-46.58842166684128,168.80490803654232</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>-46.58793709986429,168.80431267602063</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-46.587486881993456,168.803682985408</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-46.58705519871342,168.8030171485118</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-46.58668162037306,168.8022839866435</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>-46.59078815144573,168.80587654770284</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>-46.59017472952144,168.80600615231197</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>-46.589543189066205,168.80572861813636</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-46.58896608629178,168.8053750412862</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>-46.588423214280645,168.80490499418292</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>-46.58793685098257,168.80431305234177</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-46.58748643059545,168.8036836211051</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-46.58705824202377,168.8030132844701</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-46.58667931500471,168.80228669343884</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0548/nzd0548.xlsx
+++ b/data/nzd0548/nzd0548.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K521"/>
+  <dimension ref="A1:K524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20745,6 +20745,123 @@
       <c r="K521" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>320.67</v>
+      </c>
+      <c r="C522" t="n">
+        <v>313.71</v>
+      </c>
+      <c r="D522" t="n">
+        <v>335.77</v>
+      </c>
+      <c r="E522" t="n">
+        <v>323.05</v>
+      </c>
+      <c r="F522" t="n">
+        <v>320.49</v>
+      </c>
+      <c r="G522" t="n">
+        <v>314.42</v>
+      </c>
+      <c r="H522" t="n">
+        <v>309.88</v>
+      </c>
+      <c r="I522" t="n">
+        <v>309.56</v>
+      </c>
+      <c r="J522" t="n">
+        <v>309.22</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>318.98</v>
+      </c>
+      <c r="C523" t="n">
+        <v>311.8</v>
+      </c>
+      <c r="D523" t="n">
+        <v>332.98</v>
+      </c>
+      <c r="E523" t="n">
+        <v>320.31</v>
+      </c>
+      <c r="F523" t="n">
+        <v>318.74</v>
+      </c>
+      <c r="G523" t="n">
+        <v>312.82</v>
+      </c>
+      <c r="H523" t="n">
+        <v>304.67</v>
+      </c>
+      <c r="I523" t="n">
+        <v>308.06</v>
+      </c>
+      <c r="J523" t="n">
+        <v>307.2</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>317.79</v>
+      </c>
+      <c r="C524" t="n">
+        <v>310.77</v>
+      </c>
+      <c r="D524" t="n">
+        <v>332.41</v>
+      </c>
+      <c r="E524" t="n">
+        <v>319.31</v>
+      </c>
+      <c r="F524" t="n">
+        <v>318.18</v>
+      </c>
+      <c r="G524" t="n">
+        <v>311.69</v>
+      </c>
+      <c r="H524" t="n">
+        <v>303.54</v>
+      </c>
+      <c r="I524" t="n">
+        <v>307.85</v>
+      </c>
+      <c r="J524" t="n">
+        <v>307.22</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B547"/>
+  <dimension ref="A1:B550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26232,6 +26349,36 @@
       </c>
       <c r="B547" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -26400,28 +26547,28 @@
         <v>0.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3884376134504392</v>
+        <v>-0.3784649458187285</v>
       </c>
       <c r="J2" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K2" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1820609427659134</v>
+        <v>0.1745635472725501</v>
       </c>
       <c r="M2" t="n">
-        <v>4.372226784219206</v>
+        <v>4.389010648113126</v>
       </c>
       <c r="N2" t="n">
-        <v>38.14841555939795</v>
+        <v>38.37986513162467</v>
       </c>
       <c r="O2" t="n">
-        <v>6.176440363137813</v>
+        <v>6.195148515703612</v>
       </c>
       <c r="P2" t="n">
-        <v>320.7466371704064</v>
+        <v>320.6398188422372</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26478,28 +26625,28 @@
         <v>0.0852</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1456127009454706</v>
+        <v>-0.1396568440029891</v>
       </c>
       <c r="J3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04830715628694082</v>
+        <v>0.04484390322153331</v>
       </c>
       <c r="M3" t="n">
-        <v>3.823987472322107</v>
+        <v>3.831885076762533</v>
       </c>
       <c r="N3" t="n">
-        <v>23.66161742946548</v>
+        <v>23.69390196423515</v>
       </c>
       <c r="O3" t="n">
-        <v>4.864320860044645</v>
+        <v>4.867638232678672</v>
       </c>
       <c r="P3" t="n">
-        <v>310.6902522218776</v>
+        <v>310.6267579663809</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26556,28 +26703,28 @@
         <v>0.0808</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2017034692471131</v>
+        <v>-0.191650632019142</v>
       </c>
       <c r="J4" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K4" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07705562295079871</v>
+        <v>0.06981529277330711</v>
       </c>
       <c r="M4" t="n">
-        <v>4.168345196525939</v>
+        <v>4.193666609763423</v>
       </c>
       <c r="N4" t="n">
-        <v>27.60314141479029</v>
+        <v>27.91131755150896</v>
       </c>
       <c r="O4" t="n">
-        <v>5.25386918516157</v>
+        <v>5.283116272760704</v>
       </c>
       <c r="P4" t="n">
-        <v>330.1678936287211</v>
+        <v>330.0607161506931</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26634,28 +26781,28 @@
         <v>0.08119999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.231203006074205</v>
+        <v>-0.2226475092127393</v>
       </c>
       <c r="J5" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K5" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09616585927256593</v>
+        <v>0.089851396988335</v>
       </c>
       <c r="M5" t="n">
-        <v>4.199185113640731</v>
+        <v>4.218038902634535</v>
       </c>
       <c r="N5" t="n">
-        <v>28.49285487680254</v>
+        <v>28.67314899231582</v>
       </c>
       <c r="O5" t="n">
-        <v>5.337869881966264</v>
+        <v>5.354731458468839</v>
       </c>
       <c r="P5" t="n">
-        <v>319.4710361935439</v>
+        <v>319.3798360918875</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26712,28 +26859,28 @@
         <v>0.0701</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1598832352132466</v>
+        <v>-0.1522583978827841</v>
       </c>
       <c r="J6" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K6" t="n">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0510289563079187</v>
+        <v>0.04661645472155418</v>
       </c>
       <c r="M6" t="n">
-        <v>4.252599312844065</v>
+        <v>4.262832847234464</v>
       </c>
       <c r="N6" t="n">
-        <v>27.12318023091392</v>
+        <v>27.23571794507148</v>
       </c>
       <c r="O6" t="n">
-        <v>5.207991957646817</v>
+        <v>5.218785102403765</v>
       </c>
       <c r="P6" t="n">
-        <v>316.6252274973741</v>
+        <v>316.5441536383334</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26790,28 +26937,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0004441830295382435</v>
+        <v>0.00919065034331088</v>
       </c>
       <c r="J7" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K7" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L7" t="n">
-        <v>1.519581677156268e-07</v>
+        <v>6.549757858476113e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>6.777334014337643</v>
+        <v>6.778432432440571</v>
       </c>
       <c r="N7" t="n">
-        <v>73.67780184323954</v>
+        <v>73.67979058486353</v>
       </c>
       <c r="O7" t="n">
-        <v>8.583577450180055</v>
+        <v>8.583693295130221</v>
       </c>
       <c r="P7" t="n">
-        <v>304.3793425705257</v>
+        <v>304.2766866257739</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26868,28 +27015,28 @@
         <v>0.1109</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09986451155885552</v>
+        <v>0.1045914171222884</v>
       </c>
       <c r="J8" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K8" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01038532755184396</v>
+        <v>0.01149227930387864</v>
       </c>
       <c r="M8" t="n">
-        <v>5.931992366752588</v>
+        <v>5.916595342277995</v>
       </c>
       <c r="N8" t="n">
-        <v>54.02364989811114</v>
+        <v>53.85753426978177</v>
       </c>
       <c r="O8" t="n">
-        <v>7.350078223945045</v>
+        <v>7.338769261244134</v>
       </c>
       <c r="P8" t="n">
-        <v>299.1134686023512</v>
+        <v>299.0631569583597</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26946,28 +27093,28 @@
         <v>0.095</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06562996023191631</v>
+        <v>0.07714615962543199</v>
       </c>
       <c r="J9" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K9" t="n">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001960829323573998</v>
+        <v>0.002728529882016217</v>
       </c>
       <c r="M9" t="n">
-        <v>9.390295875471551</v>
+        <v>9.386449375613839</v>
       </c>
       <c r="N9" t="n">
-        <v>123.3791764625062</v>
+        <v>123.2637401723911</v>
       </c>
       <c r="O9" t="n">
-        <v>11.10761794726962</v>
+        <v>11.10242046458299</v>
       </c>
       <c r="P9" t="n">
-        <v>296.4939152246554</v>
+        <v>296.3705579201239</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27024,28 +27171,28 @@
         <v>0.1205</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1522690775308647</v>
+        <v>0.1540994236590629</v>
       </c>
       <c r="J10" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K10" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06009452979826413</v>
+        <v>0.06213264943130559</v>
       </c>
       <c r="M10" t="n">
-        <v>3.548378832993331</v>
+        <v>3.53686717028453</v>
       </c>
       <c r="N10" t="n">
-        <v>20.5415518961501</v>
+        <v>20.44394800704988</v>
       </c>
       <c r="O10" t="n">
-        <v>4.532278885522172</v>
+        <v>4.521498424974832</v>
       </c>
       <c r="P10" t="n">
-        <v>302.1442272242189</v>
+        <v>302.1247183768036</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27083,7 +27230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K521"/>
+  <dimension ref="A1:K524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56743,6 +56890,177 @@
         </is>
       </c>
     </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>-46.59078821549374,168.80587771740178</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>-46.59017475523477,168.80600667247404</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>-46.589541836478794,168.8057368621277</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>-46.5889607720156,168.80538820368528</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-46.588415850602836,168.80491947161565</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-46.58792733125595,168.8043274466229</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-46.58747398490598,168.80370114817828</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-46.58705688944141,168.80301500182202</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-46.58667840682928,168.80228775975212</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>-46.59078941817049,168.80589968174974</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>-46.590175983043444,168.8060315102133</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>-46.589536030750565,168.80577224787098</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>-46.58894832661038,168.80541902843916</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>-46.58840651260278,168.80493783067325</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>-46.58791737598414,168.8043424994605</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>-46.587440387978084,168.80374846215437</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-46.58704674507279,168.80302788195877</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-46.58666429517881,168.80230432861515</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>-46.59079026502321,168.80591514777063</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>-46.59017664515792,168.80604490438742</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>-46.58953484463266,168.8057794772155</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>-46.58894378448949,168.8054302783459</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>-46.58840352444211,168.8049437055704</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>-46.5879103450721,168.80435313052374</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>-46.58743310111754,168.80375872410303</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-46.58704532486106,168.80302968517753</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>-46.58666443489813,168.80230416456706</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
